--- a/lunar lander failures over the years.xlsx
+++ b/lunar lander failures over the years.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B9290C9-2750-4DC5-9B87-4FD27A905882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E94693-66E4-4370-A736-742FC3EA22B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-46188" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BB390FF6-EF55-43DC-9F23-A0B7CC5042FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BB390FF6-EF55-43DC-9F23-A0B7CC5042FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -507,14 +507,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -664,15 +657,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -690,39 +679,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1068,584 +1046,584 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>1963</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="12">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="D2" s="7"/>
+      <c r="E2" s="8">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>1963</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="D3" s="7"/>
+      <c r="E3" s="8">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>1963</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="D4" s="7"/>
+      <c r="E4" s="8">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>1964</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="D5" s="7"/>
+      <c r="E5" s="8">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>1964</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="12">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="D6" s="7"/>
+      <c r="E6" s="8">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>1965</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4" t="s">
+      <c r="D7" s="7"/>
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>1965</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="12">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="D8" s="7"/>
+      <c r="E8" s="8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>1965</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="s">
+      <c r="D9" s="7"/>
+      <c r="E9" s="8">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>1965</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="12">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="D10" s="7"/>
+      <c r="E10" s="8">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>1965</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="12">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="8">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>1965</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="12">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="D12" s="7"/>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="2" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="13">
+      <c r="A13" s="9">
         <v>1966</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D13" s="11">
-        <v>1</v>
-      </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="4">
+      <c r="D13" s="7">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="2">
         <v>3</v>
       </c>
-      <c r="G13" s="10"/>
-    </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13">
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="9">
         <v>1966</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="12">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4">
+      <c r="D14" s="7"/>
+      <c r="E14" s="8">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
         <v>20</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="2" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="13">
+      <c r="A15" s="9">
         <v>1966</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="11">
-        <v>1</v>
-      </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="4" t="s">
+      <c r="C15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="2" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="13">
+      <c r="A16" s="9">
         <v>1966</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="11">
-        <v>1</v>
-      </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="4" t="s">
+      <c r="D16" s="7">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="F16" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>1966</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="12">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4">
+      <c r="D17" s="7"/>
+      <c r="E17" s="8">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
         <v>21</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="13">
+      <c r="A18" s="9">
         <v>1967</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="11">
-        <v>1</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="4">
+      <c r="D18" s="7">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8"/>
+      <c r="F18" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="13">
+      <c r="A19" s="9">
         <v>1967</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="11">
-        <v>1</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="4">
+      <c r="D19" s="7">
+        <v>1</v>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="13">
+      <c r="A20" s="9">
         <v>1967</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="11">
-        <v>1</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="4">
+      <c r="D20" s="7">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="13">
+      <c r="A21" s="9">
         <v>1968</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="11">
-        <v>1</v>
-      </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="4">
+      <c r="D21" s="7">
+        <v>1</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="13">
+      <c r="A22" s="9">
         <v>1969</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="11">
-        <v>1</v>
-      </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="20">
+      <c r="D22" s="7">
+        <v>1</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="13">
+      <c r="A23" s="9">
         <v>1969</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="11">
-        <v>1</v>
-      </c>
-      <c r="E23" s="12"/>
-      <c r="F23" s="4">
+      <c r="D23" s="7">
+        <v>1</v>
+      </c>
+      <c r="E23" s="8"/>
+      <c r="F23" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="13">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="9">
         <v>1969</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="12">
-        <v>1</v>
-      </c>
-      <c r="F24" s="4">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1" t="s">
+      <c r="D24" s="7"/>
+      <c r="E24" s="8">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="13">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="9">
         <v>1969</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="12">
-        <v>1</v>
-      </c>
-      <c r="F25" s="4">
-        <v>1</v>
-      </c>
-      <c r="G25" s="1" t="s">
+      <c r="D25" s="7"/>
+      <c r="E25" s="8">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="13">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="9">
         <v>1969</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="12">
-        <v>1</v>
-      </c>
-      <c r="F26" s="4">
-        <v>1</v>
-      </c>
-      <c r="G26" s="1" t="s">
+      <c r="D26" s="7"/>
+      <c r="E26" s="8">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="13">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="9">
         <v>1969</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="12">
-        <v>1</v>
-      </c>
-      <c r="F27" s="4">
-        <v>1</v>
-      </c>
-      <c r="G27" s="1" t="s">
+      <c r="D27" s="7"/>
+      <c r="E27" s="8">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="13">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="9">
         <v>1969</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="12">
-        <v>1</v>
-      </c>
-      <c r="F28" s="4">
-        <v>1</v>
-      </c>
-      <c r="G28" s="1" t="s">
+      <c r="D28" s="7"/>
+      <c r="E28" s="8">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="13">
+      <c r="A29" s="9">
         <v>1970</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="12">
-        <v>1</v>
-      </c>
-      <c r="F29" s="4">
+      <c r="D29" s="7"/>
+      <c r="E29" s="8">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
         <v>1</v>
       </c>
       <c r="G29" t="s">
@@ -1653,284 +1631,284 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="13">
+      <c r="A30" s="9">
         <v>1970</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="11">
-        <v>1</v>
-      </c>
-      <c r="E30" s="12"/>
-      <c r="F30" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="13">
+      <c r="D30" s="7">
+        <v>1</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="9">
         <v>1970</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="11">
-        <v>1</v>
-      </c>
-      <c r="E31" s="12"/>
-      <c r="F31" s="4">
+      <c r="D31" s="7">
+        <v>1</v>
+      </c>
+      <c r="E31" s="8"/>
+      <c r="F31" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="13">
+      <c r="A32" s="9">
         <v>1970</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D32" s="11"/>
-      <c r="E32" s="12">
-        <v>1</v>
-      </c>
-      <c r="F32" s="4">
+      <c r="D32" s="7"/>
+      <c r="E32" s="8">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
         <v>4</v>
       </c>
       <c r="G32" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="13">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="9">
         <v>1971</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D33" s="11"/>
-      <c r="E33" s="12">
-        <v>1</v>
-      </c>
-      <c r="F33" s="4">
-        <v>1</v>
-      </c>
-      <c r="G33" s="1" t="s">
+      <c r="D33" s="7"/>
+      <c r="E33" s="8">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="13">
+      <c r="A34" s="9">
         <v>1971</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D34" s="11">
-        <v>1</v>
-      </c>
-      <c r="E34" s="12"/>
-      <c r="F34" s="4">
+      <c r="D34" s="7">
+        <v>1</v>
+      </c>
+      <c r="E34" s="8"/>
+      <c r="F34" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="13">
+      <c r="A35" s="9">
         <v>1971</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D35" s="11">
-        <v>1</v>
-      </c>
-      <c r="E35" s="12"/>
-      <c r="F35" s="4">
+      <c r="D35" s="7">
+        <v>1</v>
+      </c>
+      <c r="E35" s="8"/>
+      <c r="F35" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="13">
+      <c r="A36" s="9">
         <v>1972</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D36" s="11">
-        <v>1</v>
-      </c>
-      <c r="E36" s="12"/>
-      <c r="F36" s="4">
+      <c r="D36" s="7">
+        <v>1</v>
+      </c>
+      <c r="E36" s="8"/>
+      <c r="F36" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="13">
+      <c r="A37" s="9">
         <v>1972</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D37" s="11">
-        <v>1</v>
-      </c>
-      <c r="E37" s="12"/>
-      <c r="F37" s="4">
+      <c r="D37" s="7">
+        <v>1</v>
+      </c>
+      <c r="E37" s="8"/>
+      <c r="F37" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="13">
+      <c r="A38" s="9">
         <v>1972</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D38" s="11">
-        <v>1</v>
-      </c>
-      <c r="E38" s="12"/>
-      <c r="F38" s="4">
+      <c r="D38" s="7">
+        <v>1</v>
+      </c>
+      <c r="E38" s="8"/>
+      <c r="F38" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="13">
+      <c r="A39" s="9">
         <v>1973</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D39" s="11">
-        <v>1</v>
-      </c>
-      <c r="E39" s="12"/>
-      <c r="F39" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="13">
+      <c r="D39" s="7">
+        <v>1</v>
+      </c>
+      <c r="E39" s="8"/>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="9">
         <v>1975</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="11"/>
-      <c r="E40" s="12">
-        <v>1</v>
-      </c>
-      <c r="F40" s="4">
-        <v>1</v>
-      </c>
-      <c r="G40" s="1" t="s">
+      <c r="D40" s="7"/>
+      <c r="E40" s="8">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1</v>
+      </c>
+      <c r="G40" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="13">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="9">
         <v>1974</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="12">
-        <v>1</v>
-      </c>
-      <c r="F41" s="4">
-        <v>1</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="D41" s="7"/>
+      <c r="E41" s="8">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="13">
+      <c r="A42" s="9">
         <v>1976</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="11">
-        <v>1</v>
-      </c>
-      <c r="E42" s="12"/>
-      <c r="F42" s="4">
+      <c r="D42" s="7">
+        <v>1</v>
+      </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="13">
+      <c r="A43" s="9">
         <v>2013</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D43" s="11">
-        <v>1</v>
-      </c>
-      <c r="E43" s="12"/>
-      <c r="F43" s="4" t="s">
+      <c r="D43" s="7">
+        <v>1</v>
+      </c>
+      <c r="E43" s="8"/>
+      <c r="F43" s="2" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="13">
+      <c r="A44" s="9">
         <v>2019</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D44" s="11"/>
-      <c r="E44" s="12">
-        <v>1</v>
-      </c>
-      <c r="F44" s="4">
+      <c r="D44" s="7"/>
+      <c r="E44" s="8">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
         <v>7</v>
       </c>
       <c r="G44" t="s">
@@ -1938,20 +1916,20 @@
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="13">
+      <c r="A45" s="9">
         <v>2019</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D45" s="11"/>
-      <c r="E45" s="12">
-        <v>1</v>
-      </c>
-      <c r="F45" s="4">
+      <c r="D45" s="7"/>
+      <c r="E45" s="8">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
         <v>8</v>
       </c>
       <c r="G45" t="s">
@@ -1959,56 +1937,56 @@
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="13">
+      <c r="A46" s="9">
         <v>2019</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D46" s="11">
-        <v>1</v>
-      </c>
-      <c r="E46" s="12"/>
-      <c r="F46" s="4" t="s">
+      <c r="D46" s="7">
+        <v>1</v>
+      </c>
+      <c r="E46" s="8"/>
+      <c r="F46" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="13">
+      <c r="A47" s="9">
         <v>2020</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D47" s="11">
-        <v>1</v>
-      </c>
-      <c r="E47" s="12"/>
-      <c r="F47" s="4">
+      <c r="D47" s="7">
+        <v>1</v>
+      </c>
+      <c r="E47" s="8"/>
+      <c r="F47" s="2">
         <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="13">
+      <c r="A48" s="9">
         <v>2022</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D48" s="11"/>
-      <c r="E48" s="12">
-        <v>1</v>
-      </c>
-      <c r="F48" s="4">
+      <c r="D48" s="7"/>
+      <c r="E48" s="8">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2">
         <v>10</v>
       </c>
       <c r="G48" t="s">
@@ -2016,41 +1994,41 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="13">
+      <c r="A49" s="9">
         <v>2023</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="C49" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D49" s="11"/>
-      <c r="E49" s="12">
-        <v>1</v>
-      </c>
-      <c r="F49" s="4">
+      <c r="D49" s="7"/>
+      <c r="E49" s="8">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2">
         <v>11</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
+      <c r="A50" s="9">
         <v>2023</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D50" s="11"/>
-      <c r="E50" s="12">
-        <v>1</v>
-      </c>
-      <c r="F50" s="4">
+      <c r="D50" s="7"/>
+      <c r="E50" s="8">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2">
         <v>12</v>
       </c>
       <c r="G50" t="s">
@@ -2058,92 +2036,92 @@
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
+      <c r="A51" s="9">
         <v>2024</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D51" s="11">
-        <v>1</v>
-      </c>
-      <c r="E51" s="12"/>
-      <c r="F51" s="4">
+      <c r="D51" s="7">
+        <v>1</v>
+      </c>
+      <c r="E51" s="8"/>
+      <c r="F51" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="13">
+      <c r="A52" s="9">
         <v>2024</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C52" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D52" s="11">
-        <v>1</v>
-      </c>
-      <c r="E52" s="12"/>
-      <c r="F52" s="4">
+      <c r="D52" s="7">
+        <v>1</v>
+      </c>
+      <c r="E52" s="8"/>
+      <c r="F52" s="2">
         <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="13">
+      <c r="A53" s="9">
         <v>2024</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D53" s="11">
-        <v>1</v>
-      </c>
-      <c r="E53" s="12"/>
-      <c r="F53" s="4">
+      <c r="D53" s="7">
+        <v>1</v>
+      </c>
+      <c r="E53" s="8"/>
+      <c r="F53" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="13">
+      <c r="A54" s="9">
         <v>2025</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D54" s="11">
-        <v>1</v>
-      </c>
-      <c r="E54" s="12"/>
-      <c r="F54" s="4" t="s">
+      <c r="D54" s="7">
+        <v>1</v>
+      </c>
+      <c r="E54" s="8"/>
+      <c r="F54" s="2" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="13">
+      <c r="A55" s="9">
         <v>2025</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D55" s="11"/>
-      <c r="E55" s="12">
-        <v>1</v>
-      </c>
-      <c r="F55" s="4">
+      <c r="D55" s="7"/>
+      <c r="E55" s="8">
+        <v>1</v>
+      </c>
+      <c r="F55" s="2">
         <v>18</v>
       </c>
       <c r="G55" t="s">
@@ -2151,20 +2129,20 @@
       </c>
     </row>
     <row r="56" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="14">
+      <c r="A56" s="10">
         <v>2025</v>
       </c>
-      <c r="B56" s="15" t="s">
+      <c r="B56" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D56" s="17"/>
-      <c r="E56" s="16">
-        <v>1</v>
-      </c>
-      <c r="F56" s="4">
+      <c r="D56" s="13"/>
+      <c r="E56" s="12">
+        <v>1</v>
+      </c>
+      <c r="F56" s="2">
         <v>19</v>
       </c>
       <c r="G56" t="s">
@@ -2172,197 +2150,196 @@
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="8">
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="6">
         <f>SUM(D2:D56)</f>
         <v>25</v>
       </c>
-      <c r="E57" s="7">
+      <c r="E57" s="5">
         <f>SUM(E2:E56)</f>
         <v>30</v>
       </c>
-      <c r="F57" s="4"/>
+      <c r="F57" s="2"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="9" t="s">
+      <c r="A60" t="s">
         <v>87</v>
       </c>
-      <c r="B60" s="9"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
-        <v>1</v>
-      </c>
-      <c r="B61" s="1" t="s">
+      <c r="A61" s="1">
+        <v>1</v>
+      </c>
+      <c r="B61" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
+      <c r="A62" s="1">
         <v>2</v>
       </c>
-      <c r="B62" s="19" t="s">
+      <c r="B62" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
+      <c r="A63" s="1">
         <v>3</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
+      <c r="A64" s="1">
         <v>4</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
+      <c r="A65" s="1">
         <v>5</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+      <c r="A66" s="1">
         <v>6</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
+      <c r="A67" s="1">
         <v>7</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
+      <c r="A68" s="1">
         <v>8</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
+      <c r="A69" s="1">
         <v>9</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
+      <c r="A70" s="1">
         <v>10</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
+      <c r="A71" s="1">
         <v>11</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
+      <c r="A72" s="1">
         <v>12</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
+      <c r="A73" s="1">
         <v>13</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+      <c r="A74" s="1">
         <v>14</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
+      <c r="A75" s="1">
         <v>15</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
+      <c r="A76" s="1">
         <v>16</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
+      <c r="A77" s="1">
         <v>17</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
+      <c r="A78" s="1">
         <v>18</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
+      <c r="A79" s="1">
         <v>19</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
+      <c r="A80" s="1">
         <v>20</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
+      <c r="A81" s="1">
         <v>21</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B83" s="21"/>
+      <c r="B83" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lunar lander failures over the years.xlsx
+++ b/lunar lander failures over the years.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E94693-66E4-4370-A736-742FC3EA22B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73EF5C1-E1D9-438C-B320-26AA12A54CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BB390FF6-EF55-43DC-9F23-A0B7CC5042FB}"/>
+    <workbookView xWindow="30" yWindow="930" windowWidth="23010" windowHeight="12210" xr2:uid="{BB390FF6-EF55-43DC-9F23-A0B7CC5042FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="134">
   <si>
     <t>Surveyor 1</t>
   </si>
@@ -501,6 +501,12 @@
   </si>
   <si>
     <t>impacted lunar surface at high speed, laser altimeter problem</t>
+  </si>
+  <si>
+    <t>Peregrine</t>
+  </si>
+  <si>
+    <t>PM-1</t>
   </si>
 </sst>
 </file>
@@ -1036,7 +1042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF8FE64D-F86F-460A-998D-DD947BEA4F45}">
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -2040,35 +2046,33 @@
         <v>2024</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D51" s="7">
-        <v>1</v>
-      </c>
-      <c r="E51" s="8"/>
-      <c r="F51" s="2">
-        <v>13</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="D51" s="7"/>
+      <c r="E51" s="8">
+        <v>1</v>
+      </c>
+      <c r="F51" s="2"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>2024</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="D52" s="7">
         <v>1</v>
       </c>
       <c r="E52" s="8"/>
       <c r="F52" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -2076,35 +2080,35 @@
         <v>2024</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D53" s="7">
         <v>1</v>
       </c>
       <c r="E53" s="8"/>
       <c r="F53" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="D54" s="7">
         <v>1</v>
       </c>
       <c r="E54" s="8"/>
-      <c r="F54" s="2" t="s">
-        <v>108</v>
+      <c r="F54" s="2">
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -2112,234 +2116,252 @@
         <v>2025</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D55" s="7">
+        <v>1</v>
+      </c>
+      <c r="E55" s="8"/>
+      <c r="F55" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D55" s="7"/>
-      <c r="E55" s="8">
-        <v>1</v>
-      </c>
-      <c r="F55" s="2">
+      <c r="D56" s="7"/>
+      <c r="E56" s="8">
+        <v>1</v>
+      </c>
+      <c r="F56" s="2">
         <v>18</v>
       </c>
-      <c r="G55" t="s">
+      <c r="G56" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="10">
+    <row r="57" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="10">
         <v>2025</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B57" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C57" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D56" s="13"/>
-      <c r="E56" s="12">
-        <v>1</v>
-      </c>
-      <c r="F56" s="2">
+      <c r="D57" s="13"/>
+      <c r="E57" s="12">
+        <v>1</v>
+      </c>
+      <c r="F57" s="2">
         <v>19</v>
       </c>
-      <c r="G56" t="s">
+      <c r="G57" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
+    <row r="58" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="6">
-        <f>SUM(D2:D56)</f>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="6">
+        <f>SUM(D2:D57)</f>
         <v>25</v>
       </c>
-      <c r="E57" s="5">
-        <f>SUM(E2:E56)</f>
-        <v>30</v>
-      </c>
-      <c r="F57" s="2"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="E58" s="5">
+        <f>SUM(E2:E57)</f>
+        <v>31</v>
+      </c>
+      <c r="F58" s="2"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>1</v>
-      </c>
-      <c r="B61" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B63" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B64" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B65" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B66" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B67" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B70" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B71" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B72" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B74" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B76" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B77" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B79" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B80" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
+        <v>20</v>
+      </c>
+      <c r="B81" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
         <v>21</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B82" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B83" s="14"/>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B84" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
